--- a/src/assets/templates/KeyVocabulary_ImportTemplate.xlsx
+++ b/src/assets/templates/KeyVocabulary_ImportTemplate.xlsx
@@ -1,57 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Template" sheetId="1" r:id="rId2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="1" r:id="Rfd08ccf679ef4a9f"/>
   </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Từ vựng (*)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loại từ vựng (*)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phiên âm (*)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nghĩa (*)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Audio Pronunciation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hello</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Noun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/həˈləʊ/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xin chào (Mẫu)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>world</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/wɜːld/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thế giới (Mẫu)</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61,22 +18,18 @@
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
-      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -88,24 +41,29 @@
         <x:fgColor rgb="FFD9E1F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
+      <x:left style="none"/>
+      <x:right style="none"/>
+      <x:top style="none"/>
+      <x:bottom style="none"/>
+      <x:diagonal style="none"/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
@@ -116,18 +74,34 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
+  <x:cellXfs count="8">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
@@ -175,72 +149,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -296,7 +212,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -305,13 +221,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -345,17 +261,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -410,82 +315,83 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:E3"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" s="1" customFormat="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
+    <x:row r="1" s="1" customFormat="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>Từ gốc</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>Từ vựng (*)</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="str">
+        <x:v>Loại từ vựng (*)</x:v>
+      </x:c>
+      <x:c r="D1" s="7" t="str">
+        <x:v>Phiên âm (*)</x:v>
+      </x:c>
+      <x:c r="E1" s="7" t="str">
+        <x:v>Nghĩa (*)</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="str">
+        <x:v>Audio Pronunciation</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>hello</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>hello</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Noun</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>/həˈləʊ/</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>xin chào (Mẫu)</x:v>
+      </x:c>
+      <x:c r="F2" t="str"/>
     </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>world</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>world</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Noun</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>/wɜːld/</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>thế giới (Mẫu)</x:v>
+      </x:c>
+      <x:c r="F3" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B1000">
-      <x:formula1>"Noun,Verb,Adjective,Adverb,NounPhrase,PhrasalVerb,AdjectivePhrase,Idiom,VerbPhrase,Preposition,PrepositionalPhrase,Prefix,Suffix,Conjunction,Interjection,Phrase"</x:formula1>
-      <x:formula2/>
+    <x:dataValidation type="list" sqref="C2:C1000">
+      <x:formula1>"Noun,Verb,Adjective,Adverb,Noun Phrase,Phrasal Verb,Adjective Phrase,Idiom,Verb Phrase,Preposition,Prepositional Phrase,Prefix,Suffix,Conjunction,Interjection,Phrase"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>